--- a/templates/32-system-hop.xlsx
+++ b/templates/32-system-hop.xlsx
@@ -113,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -138,6 +138,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2055,10 +2058,10 @@
       </c>
     </row>
     <row r="38"/>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>STEP 1 — how much of each contact went on moving between systems</t>
+    <row r="39" ht="48" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>STEP 1 — how much of each contact went on moving between systems  ·  Key: Share of handle time = the swivel measured against the whole contact, which is the number to take to anyone who owns the handle-time target. Where 'share of hop time' ranks the pairs against each other, this one says what the hopping costs overall — the same seconds against the 412-second baseline rather than against the other hops</t>
         </is>
       </c>
       <c r="B39" s="7" t="n"/>
@@ -2114,19 +2117,19 @@
           <t>BA-2201</t>
         </is>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="17">
         <f>SUMIF($A$13:$A$36,$B41,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D41" s="17">
+      <c r="D41" s="18">
         <f>IFERROR(C41/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E41" s="18">
+      <c r="E41" s="19">
         <f>COUNTIF($A$13:$A$36,$B41)</f>
         <v/>
       </c>
-      <c r="F41" s="18">
+      <c r="F41" s="19">
         <f>COUNTIFS($A$13:$A$36,$B41,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
@@ -2142,19 +2145,19 @@
           <t>BA-2202</t>
         </is>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="17">
         <f>SUMIF($A$13:$A$36,$B42,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D42" s="17">
+      <c r="D42" s="18">
         <f>IFERROR(C42/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="19">
         <f>COUNTIF($A$13:$A$36,$B42)</f>
         <v/>
       </c>
-      <c r="F42" s="18">
+      <c r="F42" s="19">
         <f>COUNTIFS($A$13:$A$36,$B42,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
@@ -2170,19 +2173,19 @@
           <t>BA-2203</t>
         </is>
       </c>
-      <c r="C43" s="16">
+      <c r="C43" s="17">
         <f>SUMIF($A$13:$A$36,$B43,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D43" s="17">
+      <c r="D43" s="18">
         <f>IFERROR(C43/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E43" s="18">
+      <c r="E43" s="19">
         <f>COUNTIF($A$13:$A$36,$B43)</f>
         <v/>
       </c>
-      <c r="F43" s="18">
+      <c r="F43" s="19">
         <f>COUNTIFS($A$13:$A$36,$B43,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
@@ -2198,19 +2201,19 @@
           <t>BA-2204</t>
         </is>
       </c>
-      <c r="C44" s="16">
+      <c r="C44" s="17">
         <f>SUMIF($A$13:$A$36,$B44,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D44" s="17">
+      <c r="D44" s="18">
         <f>IFERROR(C44/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="19">
         <f>COUNTIF($A$13:$A$36,$B44)</f>
         <v/>
       </c>
-      <c r="F44" s="18">
+      <c r="F44" s="19">
         <f>COUNTIFS($A$13:$A$36,$B44,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
@@ -2226,19 +2229,19 @@
           <t>BA-2205</t>
         </is>
       </c>
-      <c r="C45" s="16">
+      <c r="C45" s="17">
         <f>SUMIF($A$13:$A$36,$B45,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D45" s="17">
+      <c r="D45" s="18">
         <f>IFERROR(C45/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="19">
         <f>COUNTIF($A$13:$A$36,$B45)</f>
         <v/>
       </c>
-      <c r="F45" s="18">
+      <c r="F45" s="19">
         <f>COUNTIFS($A$13:$A$36,$B45,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
@@ -2254,19 +2257,19 @@
           <t>BA-2206</t>
         </is>
       </c>
-      <c r="C46" s="16">
+      <c r="C46" s="17">
         <f>SUMIF($A$13:$A$36,$B46,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D46" s="17">
+      <c r="D46" s="18">
         <f>IFERROR(C46/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="19">
         <f>COUNTIF($A$13:$A$36,$B46)</f>
         <v/>
       </c>
-      <c r="F46" s="18">
+      <c r="F46" s="19">
         <f>COUNTIFS($A$13:$A$36,$B46,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
@@ -2299,7 +2302,7 @@
           <t>Contacts observed</t>
         </is>
       </c>
-      <c r="B50" s="18">
+      <c r="B50" s="19">
         <f>COUNTA($B$41:$B$46)</f>
         <v/>
       </c>
@@ -2315,7 +2318,7 @@
           <t>Hops logged</t>
         </is>
       </c>
-      <c r="B51" s="18">
+      <c r="B51" s="19">
         <f>SUM($E$41:$E$46)</f>
         <v/>
       </c>
@@ -2331,7 +2334,7 @@
           <t>Hops per contact</t>
         </is>
       </c>
-      <c r="B52" s="19">
+      <c r="B52" s="20">
         <f>IFERROR(B51/B50,"")</f>
         <v/>
       </c>
@@ -2347,7 +2350,7 @@
           <t>Seconds per contact spent hopping</t>
         </is>
       </c>
-      <c r="B53" s="18">
+      <c r="B53" s="19">
         <f>IFERROR(SUM($C$41:$C$46)/B50,"")</f>
         <v/>
       </c>
@@ -2363,7 +2366,7 @@
           <t>Share of handle time</t>
         </is>
       </c>
-      <c r="B54" s="17">
+      <c r="B54" s="18">
         <f>IFERROR(B53/B7,"")</f>
         <v/>
       </c>
@@ -2379,7 +2382,7 @@
           <t>Share of hops that re-key data</t>
         </is>
       </c>
-      <c r="B55" s="17">
+      <c r="B55" s="18">
         <f>IFERROR(SUM($F$41:$F$46)/B51,"")</f>
         <v/>
       </c>
@@ -2395,7 +2398,7 @@
           <t>Agent hours a year spent hopping</t>
         </is>
       </c>
-      <c r="B56" s="16">
+      <c r="B56" s="17">
         <f>IFERROR(B53*B8/3600,"")</f>
         <v/>
       </c>
@@ -2411,7 +2414,7 @@
           <t>What that time costs a year</t>
         </is>
       </c>
-      <c r="B57" s="20">
+      <c r="B57" s="21">
         <f>IFERROR(B56*B9,"")</f>
         <v/>
       </c>
@@ -2429,10 +2432,10 @@
       </c>
     </row>
     <row r="59"/>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>STEP 3 — which hop to attack</t>
+    <row r="60" ht="48" customHeight="1">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>STEP 3 — which hop to attack  ·  Key: Share of hop time = that system pair's seconds as a percentage of all the time spent moving between systems — a share of the SWIVEL, not of the contact. Case tool to Billing platform takes 198 of the 737 logged seconds, 26.9% (E62, G62), so a third of the swivelling happens on one pair. It is the column that says which integration to build first</t>
         </is>
       </c>
       <c r="B60" s="7" t="n"/>
@@ -2496,27 +2499,27 @@
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="C62" s="21">
+      <c r="C62" s="22">
         <f>IF($A62="","",$A62&amp;" → "&amp;$B62)</f>
         <v/>
       </c>
-      <c r="D62" s="18">
+      <c r="D62" s="19">
         <f>COUNTIFS($C$13:$C$36,$A62,$D$13:$D$36,$B62)</f>
         <v/>
       </c>
-      <c r="E62" s="16">
+      <c r="E62" s="17">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A62,$D$13:$D$36,$B62)</f>
         <v/>
       </c>
-      <c r="F62" s="19">
+      <c r="F62" s="20">
         <f>IFERROR(E62/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G62" s="17">
+      <c r="G62" s="18">
         <f>IFERROR(E62/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H62" s="21">
+      <c r="H62" s="22">
         <f>IF(COUNTIFS($C$13:$C$36,$A62,$D$13:$D$36,$B62,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
@@ -2532,27 +2535,27 @@
           <t>Payment gateway</t>
         </is>
       </c>
-      <c r="C63" s="21">
+      <c r="C63" s="22">
         <f>IF($A63="","",$A63&amp;" → "&amp;$B63)</f>
         <v/>
       </c>
-      <c r="D63" s="18">
+      <c r="D63" s="19">
         <f>COUNTIFS($C$13:$C$36,$A63,$D$13:$D$36,$B63)</f>
         <v/>
       </c>
-      <c r="E63" s="16">
+      <c r="E63" s="17">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A63,$D$13:$D$36,$B63)</f>
         <v/>
       </c>
-      <c r="F63" s="19">
+      <c r="F63" s="20">
         <f>IFERROR(E63/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G63" s="17">
+      <c r="G63" s="18">
         <f>IFERROR(E63/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H63" s="21">
+      <c r="H63" s="22">
         <f>IF(COUNTIFS($C$13:$C$36,$A63,$D$13:$D$36,$B63,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
@@ -2568,27 +2571,27 @@
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="C64" s="21">
+      <c r="C64" s="22">
         <f>IF($A64="","",$A64&amp;" → "&amp;$B64)</f>
         <v/>
       </c>
-      <c r="D64" s="18">
+      <c r="D64" s="19">
         <f>COUNTIFS($C$13:$C$36,$A64,$D$13:$D$36,$B64)</f>
         <v/>
       </c>
-      <c r="E64" s="16">
+      <c r="E64" s="17">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A64,$D$13:$D$36,$B64)</f>
         <v/>
       </c>
-      <c r="F64" s="19">
+      <c r="F64" s="20">
         <f>IFERROR(E64/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G64" s="17">
+      <c r="G64" s="18">
         <f>IFERROR(E64/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H64" s="21">
+      <c r="H64" s="22">
         <f>IF(COUNTIFS($C$13:$C$36,$A64,$D$13:$D$36,$B64,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
@@ -2604,27 +2607,27 @@
           <t>Case tool</t>
         </is>
       </c>
-      <c r="C65" s="21">
+      <c r="C65" s="22">
         <f>IF($A65="","",$A65&amp;" → "&amp;$B65)</f>
         <v/>
       </c>
-      <c r="D65" s="18">
+      <c r="D65" s="19">
         <f>COUNTIFS($C$13:$C$36,$A65,$D$13:$D$36,$B65)</f>
         <v/>
       </c>
-      <c r="E65" s="16">
+      <c r="E65" s="17">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A65,$D$13:$D$36,$B65)</f>
         <v/>
       </c>
-      <c r="F65" s="19">
+      <c r="F65" s="20">
         <f>IFERROR(E65/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G65" s="17">
+      <c r="G65" s="18">
         <f>IFERROR(E65/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H65" s="21">
+      <c r="H65" s="22">
         <f>IF(COUNTIFS($C$13:$C$36,$A65,$D$13:$D$36,$B65,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
@@ -2640,27 +2643,27 @@
           <t>Knowledge base</t>
         </is>
       </c>
-      <c r="C66" s="21">
+      <c r="C66" s="22">
         <f>IF($A66="","",$A66&amp;" → "&amp;$B66)</f>
         <v/>
       </c>
-      <c r="D66" s="18">
+      <c r="D66" s="19">
         <f>COUNTIFS($C$13:$C$36,$A66,$D$13:$D$36,$B66)</f>
         <v/>
       </c>
-      <c r="E66" s="16">
+      <c r="E66" s="17">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A66,$D$13:$D$36,$B66)</f>
         <v/>
       </c>
-      <c r="F66" s="19">
+      <c r="F66" s="20">
         <f>IFERROR(E66/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G66" s="17">
+      <c r="G66" s="18">
         <f>IFERROR(E66/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H66" s="21">
+      <c r="H66" s="22">
         <f>IF(COUNTIFS($C$13:$C$36,$A66,$D$13:$D$36,$B66,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
@@ -2676,27 +2679,27 @@
           <t>Case tool</t>
         </is>
       </c>
-      <c r="C67" s="21">
+      <c r="C67" s="22">
         <f>IF($A67="","",$A67&amp;" → "&amp;$B67)</f>
         <v/>
       </c>
-      <c r="D67" s="18">
+      <c r="D67" s="19">
         <f>COUNTIFS($C$13:$C$36,$A67,$D$13:$D$36,$B67)</f>
         <v/>
       </c>
-      <c r="E67" s="16">
+      <c r="E67" s="17">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A67,$D$13:$D$36,$B67)</f>
         <v/>
       </c>
-      <c r="F67" s="19">
+      <c r="F67" s="20">
         <f>IFERROR(E67/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G67" s="17">
+      <c r="G67" s="18">
         <f>IFERROR(E67/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H67" s="21">
+      <c r="H67" s="22">
         <f>IF(COUNTIFS($C$13:$C$36,$A67,$D$13:$D$36,$B67,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
@@ -2729,7 +2732,7 @@
           <t>The pair costing the most time</t>
         </is>
       </c>
-      <c r="B71" s="21">
+      <c r="B71" s="22">
         <f>IFERROR(INDEX($C$62:$C$67,MATCH(MAX($E$62:$E$67),$E$62:$E$67,0)),"")</f>
         <v/>
       </c>
@@ -2745,7 +2748,7 @@
           <t>What that one pair costs a year</t>
         </is>
       </c>
-      <c r="B72" s="20">
+      <c r="B72" s="21">
         <f>IFERROR(MAX($E$62:$E$67)/B50*B8/3600*B9,"")</f>
         <v/>
       </c>
@@ -2761,7 +2764,7 @@
           <t>Does that pair re-key data?</t>
         </is>
       </c>
-      <c r="B73" s="21">
+      <c r="B73" s="22">
         <f>IFERROR(INDEX($H$62:$H$67,MATCH(MAX($E$62:$E$67),$E$62:$E$67,0)),"")</f>
         <v/>
       </c>

--- a/templates/32-system-hop.xlsx
+++ b/templates/32-system-hop.xlsx
@@ -2058,10 +2058,11 @@
       </c>
     </row>
     <row r="38"/>
-    <row r="39" ht="48" customHeight="1">
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>STEP 1 — how much of each contact went on moving between systems  ·  Key: Share of handle time = the swivel measured against the whole contact, which is the number to take to anyone who owns the handle-time target. Where 'share of hop time' ranks the pairs against each other, this one says what the hopping costs overall — the same seconds against the 412-second baseline rather than against the other hops</t>
+          <t>STEP 1 — how much of each contact went on moving between systems  ·  Key:
+• Share of handle time = the swivel measured against the whole contact, which is the number to take to anyone who owns the handle-time target. Where 'share of hop time' ranks the pairs against each other, this one says what the hopping costs overall — the same seconds against the 412-second baseline rather than against the other hops</t>
         </is>
       </c>
       <c r="B39" s="7" t="n"/>
@@ -2432,10 +2433,11 @@
       </c>
     </row>
     <row r="59"/>
-    <row r="60" ht="48" customHeight="1">
+    <row r="60" ht="60" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>STEP 3 — which hop to attack  ·  Key: Share of hop time = that system pair's seconds as a percentage of all the time spent moving between systems — a share of the SWIVEL, not of the contact. Case tool to Billing platform takes 198 of the 737 logged seconds, 26.9% (E62, G62), so a third of the swivelling happens on one pair. It is the column that says which integration to build first</t>
+          <t>STEP 3 — which hop to attack  ·  Key:
+• Share of hop time = that system pair's seconds as a percentage of all the time spent moving between systems — a share of the SWIVEL, not of the contact. Case tool to Billing platform takes 198 of the 737 logged seconds, 26.9% (E62, G62), so a third of the swivelling happens on one pair. It is the column that says which integration to build first</t>
         </is>
       </c>
       <c r="B60" s="7" t="n"/>

--- a/templates/32-system-hop.xlsx
+++ b/templates/32-system-hop.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +56,11 @@
     </font>
     <font>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF4B5563"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -113,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -138,6 +143,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -446,7 +454,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>11</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -468,7 +476,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>11</col>
       <colOff>0</colOff>
       <row>20</row>
       <rowOff>0</rowOff>
@@ -953,7 +961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:R74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -964,6 +972,15 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1442,7 +1459,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="14" t="inlineStr">
         <is>
           <t>BA-2203</t>
@@ -1479,6 +1496,12 @@
           <t>—</t>
         </is>
       </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Ranked by total seconds, so the top bar is the integration to build first. The heaviest pair here takes 198 of 737 logged seconds — 26.9% of all the swivelling on one pair. Check the re-key column beside it: a hop that re-types data is both the waste and a defect opportunity.
+SO:  Build the integration for the top pair first — 26.9% of all swivel time sits on one of them. Where the re-key column is ticked, count the defect opportunity in the FMEA too, because re-typing is both waste and a failure mode.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
@@ -2050,16 +2073,22 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="90" customHeight="1">
+    <row r="37" ht="66" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
           <t>Time the hop, not the task. The seconds here are the ones between leaving one screen and being able to work in the next — the load, the second login, the search that finds the account again. The work the agent does once they arrive is not a hop and belongs in the handle time above. DATA RE-KEYED means the agent typed something into the second system that the first one already knew, which is both the waste and the defect: every re-key is a chance to mistype an account number.</t>
+        </is>
+      </c>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  One bar per contact, so the shape tells you whether the swivel is universal or concentrated. Even bars mean every contact pays it and the fix is worth the whole volume; a few tall bars mean a subset of cases is doing something the others are not, and that subset is the thing to define.
+SO:  Even bars mean fix it for everyone and size the benefit on full volume. A few tall bars mean define what those contacts have in common before building anything.</t>
         </is>
       </c>
     </row>
     <row r="38"/>
     <row r="39" ht="60" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>STEP 1 — how much of each contact went on moving between systems  ·  Key:
 • Share of handle time = the swivel measured against the whole contact, which is the number to take to anyone who owns the handle-time target. Where 'share of hop time' ranks the pairs against each other, this one says what the hopping costs overall — the same seconds against the 412-second baseline rather than against the other hops</t>
@@ -2118,19 +2147,19 @@
           <t>BA-2201</t>
         </is>
       </c>
-      <c r="C41" s="17">
+      <c r="C41" s="18">
         <f>SUMIF($A$13:$A$36,$B41,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D41" s="18">
+      <c r="D41" s="19">
         <f>IFERROR(C41/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E41" s="19">
+      <c r="E41" s="20">
         <f>COUNTIF($A$13:$A$36,$B41)</f>
         <v/>
       </c>
-      <c r="F41" s="19">
+      <c r="F41" s="20">
         <f>COUNTIFS($A$13:$A$36,$B41,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
@@ -2146,19 +2175,19 @@
           <t>BA-2202</t>
         </is>
       </c>
-      <c r="C42" s="17">
+      <c r="C42" s="18">
         <f>SUMIF($A$13:$A$36,$B42,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D42" s="18">
+      <c r="D42" s="19">
         <f>IFERROR(C42/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E42" s="19">
+      <c r="E42" s="20">
         <f>COUNTIF($A$13:$A$36,$B42)</f>
         <v/>
       </c>
-      <c r="F42" s="19">
+      <c r="F42" s="20">
         <f>COUNTIFS($A$13:$A$36,$B42,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
@@ -2174,19 +2203,19 @@
           <t>BA-2203</t>
         </is>
       </c>
-      <c r="C43" s="17">
+      <c r="C43" s="18">
         <f>SUMIF($A$13:$A$36,$B43,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D43" s="18">
+      <c r="D43" s="19">
         <f>IFERROR(C43/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E43" s="19">
+      <c r="E43" s="20">
         <f>COUNTIF($A$13:$A$36,$B43)</f>
         <v/>
       </c>
-      <c r="F43" s="19">
+      <c r="F43" s="20">
         <f>COUNTIFS($A$13:$A$36,$B43,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
@@ -2202,19 +2231,19 @@
           <t>BA-2204</t>
         </is>
       </c>
-      <c r="C44" s="17">
+      <c r="C44" s="18">
         <f>SUMIF($A$13:$A$36,$B44,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D44" s="18">
+      <c r="D44" s="19">
         <f>IFERROR(C44/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E44" s="19">
+      <c r="E44" s="20">
         <f>COUNTIF($A$13:$A$36,$B44)</f>
         <v/>
       </c>
-      <c r="F44" s="19">
+      <c r="F44" s="20">
         <f>COUNTIFS($A$13:$A$36,$B44,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
@@ -2230,19 +2259,19 @@
           <t>BA-2205</t>
         </is>
       </c>
-      <c r="C45" s="17">
+      <c r="C45" s="18">
         <f>SUMIF($A$13:$A$36,$B45,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D45" s="18">
+      <c r="D45" s="19">
         <f>IFERROR(C45/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E45" s="19">
+      <c r="E45" s="20">
         <f>COUNTIF($A$13:$A$36,$B45)</f>
         <v/>
       </c>
-      <c r="F45" s="19">
+      <c r="F45" s="20">
         <f>COUNTIFS($A$13:$A$36,$B45,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
@@ -2258,19 +2287,19 @@
           <t>BA-2206</t>
         </is>
       </c>
-      <c r="C46" s="17">
+      <c r="C46" s="18">
         <f>SUMIF($A$13:$A$36,$B46,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D46" s="18">
+      <c r="D46" s="19">
         <f>IFERROR(C46/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E46" s="19">
+      <c r="E46" s="20">
         <f>COUNTIF($A$13:$A$36,$B46)</f>
         <v/>
       </c>
-      <c r="F46" s="19">
+      <c r="F46" s="20">
         <f>COUNTIFS($A$13:$A$36,$B46,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
@@ -2303,7 +2332,7 @@
           <t>Contacts observed</t>
         </is>
       </c>
-      <c r="B50" s="19">
+      <c r="B50" s="20">
         <f>COUNTA($B$41:$B$46)</f>
         <v/>
       </c>
@@ -2319,7 +2348,7 @@
           <t>Hops logged</t>
         </is>
       </c>
-      <c r="B51" s="19">
+      <c r="B51" s="20">
         <f>SUM($E$41:$E$46)</f>
         <v/>
       </c>
@@ -2335,7 +2364,7 @@
           <t>Hops per contact</t>
         </is>
       </c>
-      <c r="B52" s="20">
+      <c r="B52" s="21">
         <f>IFERROR(B51/B50,"")</f>
         <v/>
       </c>
@@ -2351,7 +2380,7 @@
           <t>Seconds per contact spent hopping</t>
         </is>
       </c>
-      <c r="B53" s="19">
+      <c r="B53" s="20">
         <f>IFERROR(SUM($C$41:$C$46)/B50,"")</f>
         <v/>
       </c>
@@ -2367,7 +2396,7 @@
           <t>Share of handle time</t>
         </is>
       </c>
-      <c r="B54" s="18">
+      <c r="B54" s="19">
         <f>IFERROR(B53/B7,"")</f>
         <v/>
       </c>
@@ -2383,7 +2412,7 @@
           <t>Share of hops that re-key data</t>
         </is>
       </c>
-      <c r="B55" s="18">
+      <c r="B55" s="19">
         <f>IFERROR(SUM($F$41:$F$46)/B51,"")</f>
         <v/>
       </c>
@@ -2399,7 +2428,7 @@
           <t>Agent hours a year spent hopping</t>
         </is>
       </c>
-      <c r="B56" s="17">
+      <c r="B56" s="18">
         <f>IFERROR(B53*B8/3600,"")</f>
         <v/>
       </c>
@@ -2415,7 +2444,7 @@
           <t>What that time costs a year</t>
         </is>
       </c>
-      <c r="B57" s="21">
+      <c r="B57" s="22">
         <f>IFERROR(B56*B9,"")</f>
         <v/>
       </c>
@@ -2434,7 +2463,7 @@
     </row>
     <row r="59"/>
     <row r="60" ht="60" customHeight="1">
-      <c r="A60" s="16" t="inlineStr">
+      <c r="A60" s="17" t="inlineStr">
         <is>
           <t>STEP 3 — which hop to attack  ·  Key:
 • Share of hop time = that system pair's seconds as a percentage of all the time spent moving between systems — a share of the SWIVEL, not of the contact. Case tool to Billing platform takes 198 of the 737 logged seconds, 26.9% (E62, G62), so a third of the swivelling happens on one pair. It is the column that says which integration to build first</t>
@@ -2501,27 +2530,27 @@
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="C62" s="22">
+      <c r="C62" s="23">
         <f>IF($A62="","",$A62&amp;" → "&amp;$B62)</f>
         <v/>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="20">
         <f>COUNTIFS($C$13:$C$36,$A62,$D$13:$D$36,$B62)</f>
         <v/>
       </c>
-      <c r="E62" s="17">
+      <c r="E62" s="18">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A62,$D$13:$D$36,$B62)</f>
         <v/>
       </c>
-      <c r="F62" s="20">
+      <c r="F62" s="21">
         <f>IFERROR(E62/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G62" s="18">
+      <c r="G62" s="19">
         <f>IFERROR(E62/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H62" s="22">
+      <c r="H62" s="23">
         <f>IF(COUNTIFS($C$13:$C$36,$A62,$D$13:$D$36,$B62,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
@@ -2537,27 +2566,27 @@
           <t>Payment gateway</t>
         </is>
       </c>
-      <c r="C63" s="22">
+      <c r="C63" s="23">
         <f>IF($A63="","",$A63&amp;" → "&amp;$B63)</f>
         <v/>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="20">
         <f>COUNTIFS($C$13:$C$36,$A63,$D$13:$D$36,$B63)</f>
         <v/>
       </c>
-      <c r="E63" s="17">
+      <c r="E63" s="18">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A63,$D$13:$D$36,$B63)</f>
         <v/>
       </c>
-      <c r="F63" s="20">
+      <c r="F63" s="21">
         <f>IFERROR(E63/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G63" s="18">
+      <c r="G63" s="19">
         <f>IFERROR(E63/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H63" s="22">
+      <c r="H63" s="23">
         <f>IF(COUNTIFS($C$13:$C$36,$A63,$D$13:$D$36,$B63,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
@@ -2573,27 +2602,27 @@
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="C64" s="22">
+      <c r="C64" s="23">
         <f>IF($A64="","",$A64&amp;" → "&amp;$B64)</f>
         <v/>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="20">
         <f>COUNTIFS($C$13:$C$36,$A64,$D$13:$D$36,$B64)</f>
         <v/>
       </c>
-      <c r="E64" s="17">
+      <c r="E64" s="18">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A64,$D$13:$D$36,$B64)</f>
         <v/>
       </c>
-      <c r="F64" s="20">
+      <c r="F64" s="21">
         <f>IFERROR(E64/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G64" s="18">
+      <c r="G64" s="19">
         <f>IFERROR(E64/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H64" s="22">
+      <c r="H64" s="23">
         <f>IF(COUNTIFS($C$13:$C$36,$A64,$D$13:$D$36,$B64,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
@@ -2609,27 +2638,27 @@
           <t>Case tool</t>
         </is>
       </c>
-      <c r="C65" s="22">
+      <c r="C65" s="23">
         <f>IF($A65="","",$A65&amp;" → "&amp;$B65)</f>
         <v/>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="20">
         <f>COUNTIFS($C$13:$C$36,$A65,$D$13:$D$36,$B65)</f>
         <v/>
       </c>
-      <c r="E65" s="17">
+      <c r="E65" s="18">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A65,$D$13:$D$36,$B65)</f>
         <v/>
       </c>
-      <c r="F65" s="20">
+      <c r="F65" s="21">
         <f>IFERROR(E65/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G65" s="18">
+      <c r="G65" s="19">
         <f>IFERROR(E65/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H65" s="22">
+      <c r="H65" s="23">
         <f>IF(COUNTIFS($C$13:$C$36,$A65,$D$13:$D$36,$B65,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
@@ -2645,27 +2674,27 @@
           <t>Knowledge base</t>
         </is>
       </c>
-      <c r="C66" s="22">
+      <c r="C66" s="23">
         <f>IF($A66="","",$A66&amp;" → "&amp;$B66)</f>
         <v/>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="20">
         <f>COUNTIFS($C$13:$C$36,$A66,$D$13:$D$36,$B66)</f>
         <v/>
       </c>
-      <c r="E66" s="17">
+      <c r="E66" s="18">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A66,$D$13:$D$36,$B66)</f>
         <v/>
       </c>
-      <c r="F66" s="20">
+      <c r="F66" s="21">
         <f>IFERROR(E66/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G66" s="18">
+      <c r="G66" s="19">
         <f>IFERROR(E66/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H66" s="22">
+      <c r="H66" s="23">
         <f>IF(COUNTIFS($C$13:$C$36,$A66,$D$13:$D$36,$B66,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
@@ -2681,27 +2710,27 @@
           <t>Case tool</t>
         </is>
       </c>
-      <c r="C67" s="22">
+      <c r="C67" s="23">
         <f>IF($A67="","",$A67&amp;" → "&amp;$B67)</f>
         <v/>
       </c>
-      <c r="D67" s="19">
+      <c r="D67" s="20">
         <f>COUNTIFS($C$13:$C$36,$A67,$D$13:$D$36,$B67)</f>
         <v/>
       </c>
-      <c r="E67" s="17">
+      <c r="E67" s="18">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A67,$D$13:$D$36,$B67)</f>
         <v/>
       </c>
-      <c r="F67" s="20">
+      <c r="F67" s="21">
         <f>IFERROR(E67/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G67" s="18">
+      <c r="G67" s="19">
         <f>IFERROR(E67/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H67" s="22">
+      <c r="H67" s="23">
         <f>IF(COUNTIFS($C$13:$C$36,$A67,$D$13:$D$36,$B67,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
@@ -2734,7 +2763,7 @@
           <t>The pair costing the most time</t>
         </is>
       </c>
-      <c r="B71" s="22">
+      <c r="B71" s="23">
         <f>IFERROR(INDEX($C$62:$C$67,MATCH(MAX($E$62:$E$67),$E$62:$E$67,0)),"")</f>
         <v/>
       </c>
@@ -2750,7 +2779,7 @@
           <t>What that one pair costs a year</t>
         </is>
       </c>
-      <c r="B72" s="21">
+      <c r="B72" s="22">
         <f>IFERROR(MAX($E$62:$E$67)/B50*B8/3600*B9,"")</f>
         <v/>
       </c>
@@ -2766,7 +2795,7 @@
           <t>Does that pair re-key data?</t>
         </is>
       </c>
-      <c r="B73" s="22">
+      <c r="B73" s="23">
         <f>IFERROR(INDEX($H$62:$H$67,MATCH(MAX($E$62:$E$67),$E$62:$E$67,0)),"")</f>
         <v/>
       </c>
@@ -2784,7 +2813,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="31">
     <mergeCell ref="C54:H54"/>
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="C55:H55"/>
@@ -2802,6 +2831,7 @@
     <mergeCell ref="C8:H8"/>
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="C7:H7"/>
+    <mergeCell ref="J21:R21"/>
     <mergeCell ref="C72:H72"/>
     <mergeCell ref="A74:H74"/>
     <mergeCell ref="C57:H57"/>
@@ -2811,6 +2841,7 @@
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="C5:H5"/>
+    <mergeCell ref="J37:R37"/>
     <mergeCell ref="A68:H68"/>
     <mergeCell ref="C73:H73"/>
     <mergeCell ref="A58:H58"/>

--- a/templates/32-system-hop.xlsx
+++ b/templates/32-system-hop.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,6 +61,10 @@
       <i val="1"/>
       <color rgb="FF4B5563"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -118,12 +122,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -143,9 +153,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -788,11 +795,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="108" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -924,9 +937,27 @@
     </row>
     <row r="20"/>
     <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>WHAT THE COLUMNS MEAN — the short version sits above each table; this is the same thing with the worked example</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Share of handle time = the swivel measured against the whole contact, which is the number to take to anyone who owns the handle-time target. Where 'share of hop time' ranks the pairs against each other, this one says what the hopping costs overall — the same seconds against the 412-second baseline rather than against the other hops</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Share of hop time = that system pair's seconds as a percentage of all the time spent moving between systems — a share of the SWIVEL, not of the contact. Case tool to Billing platform takes 198 of the 737 logged seconds, 26.9% (E62, G62), so a third of the swivelling happens on one pair. It is the column that says which integration to build first</t>
+        </is>
+      </c>
+    </row>
     <row r="25"/>
     <row r="26"/>
     <row r="27"/>
@@ -944,10 +975,13 @@
     <row r="39"/>
     <row r="40"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
+    <mergeCell ref="B17"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="B11"/>
+    <mergeCell ref="A23:H23"/>
     <mergeCell ref="B19"/>
-    <mergeCell ref="B17"/>
-    <mergeCell ref="B11"/>
+    <mergeCell ref="A22:H22"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -984,21 +1018,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>System-hop log — what the swivel chair costs</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-      <c r="C1" s="4" t="n"/>
-      <c r="D1" s="4" t="n"/>
-      <c r="E1" s="4" t="n"/>
-      <c r="F1" s="4" t="n"/>
-      <c r="G1" s="4" t="n"/>
-      <c r="H1" s="4" t="n"/>
+      <c r="B1" s="6" t="n"/>
+      <c r="C1" s="6" t="n"/>
+      <c r="D1" s="6" t="n"/>
+      <c r="E1" s="6" t="n"/>
+      <c r="F1" s="6" t="n"/>
+      <c r="G1" s="6" t="n"/>
+      <c r="H1" s="6" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>One row per move between systems, timed at the desk. Handle time hides this: the contact takes seven minutes and nobody can say how much of it was the agent waiting for a second screen to load and typing the account number into it again. The green block is a worked example — replace it with your own observations.</t>
         </is>
@@ -1006,93 +1040,93 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>THE QUESTION — what you watched, and what counts</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="9" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Process observed</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Billing adjustment, end to end</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>One contact type. Hop counts are not comparable across contact types, and averaging them together produces a number that describes nothing anybody does.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>What counts as a hop</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Any move to a different application window</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Write the rule down before you start counting, because the borderline cases decide the answer. Tabs inside the same application: your call — but make the same call every time, and record which way you called it.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Mean handle time for this contact type (seconds)</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="13" t="n">
         <v>412</v>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>From the platform, over the same period you observed. It is the denominator for everything below, so take it from a report rather than from the six contacts you happened to watch.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Contacts of this type per year</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="13" t="n">
         <v>11592</v>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>The population the hops apply to. Adjustments here, not the whole billing queue — annualising against a population you did not observe is how a swivel-chair saving becomes a number Finance rejects.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Loaded cost per agent hour</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Salary, employer costs, benefits and paid non-productive time, divided by paid hours. Your Finance partner has this figure; do not build one.</t>
         </is>
@@ -1100,403 +1134,403 @@
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>THE LOG — one row per move, in the order the agent made them</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Contact ref</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>From system</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>To system</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>Why the agent moved</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>Seconds</t>
         </is>
       </c>
-      <c r="G12" s="13" t="inlineStr">
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>Data re-keyed?</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t>Which fields were re-keyed</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>BA-2201</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>Find the adjustment on the account</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n">
+      <c r="F13" s="17" t="n">
         <v>34</v>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>Account number</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>BA-2201</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Payment gateway</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>Check whether the refund has actually posted</t>
         </is>
       </c>
-      <c r="F14" s="15" t="n">
+      <c r="F14" s="17" t="n">
         <v>41</v>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="16" t="inlineStr">
         <is>
           <t>Transaction ID</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>BA-2201</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n">
+      <c r="B15" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>Payment gateway</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>Record the posting reference against the adjustment</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n">
+      <c r="F15" s="17" t="n">
         <v>22</v>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>Posting reference</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>BA-2201</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
+      <c r="B16" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Write the case note and close</t>
         </is>
       </c>
-      <c r="F16" s="15" t="n">
+      <c r="F16" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="16" t="inlineStr">
         <is>
           <t>Adjustment amount</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>BA-2202</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B17" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>Find the adjustment on the account</t>
         </is>
       </c>
-      <c r="F17" s="15" t="n">
+      <c r="F17" s="17" t="n">
         <v>31</v>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>Account number</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>BA-2202</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B18" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Payment gateway</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>Check whether the refund has actually posted</t>
         </is>
       </c>
-      <c r="F18" s="15" t="n">
+      <c r="F18" s="17" t="n">
         <v>38</v>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr">
         <is>
           <t>Transaction ID</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>BA-2202</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>Payment gateway</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>Record the posting reference against the adjustment</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n">
+      <c r="F19" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>Posting reference</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>BA-2202</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
+      <c r="B20" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>Write the case note and close</t>
         </is>
       </c>
-      <c r="F20" s="15" t="n">
+      <c r="F20" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="H20" s="16" t="inlineStr">
         <is>
           <t>Adjustment amount</t>
         </is>
       </c>
     </row>
     <row r="21" ht="66" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>BA-2203</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n">
+      <c r="B21" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>Knowledge base</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>Check whether this adjustment type needs a manager</t>
         </is>
       </c>
-      <c r="F21" s="15" t="n">
+      <c r="F21" s="17" t="n">
         <v>46</v>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H21" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>HOW TO READ IT.  Ranked by total seconds, so the top bar is the integration to build first. The heaviest pair here takes 198 of 737 logged seconds — 26.9% of all the swivelling on one pair. Check the re-key column beside it: a hop that re-types data is both the waste and a defect opportunity.
 SO:  Build the integration for the top pair first — 26.9% of all swivel time sits on one of them. Where the re-key column is ticked, count the defect opportunity in the FMEA too, because re-typing is both waste and a failure mode.</t>
@@ -1504,582 +1538,582 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>BA-2203</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n">
+      <c r="B22" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>Knowledge base</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Back to the case</t>
         </is>
       </c>
-      <c r="F22" s="15" t="n">
+      <c r="F22" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr">
+      <c r="H22" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>BA-2203</t>
         </is>
       </c>
-      <c r="B23" s="14" t="n">
+      <c r="B23" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>Find the adjustment on the account</t>
         </is>
       </c>
-      <c r="F23" s="15" t="n">
+      <c r="F23" s="17" t="n">
         <v>36</v>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H23" s="16" t="inlineStr">
         <is>
           <t>Account number</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>BA-2203</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
+      <c r="B24" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>Write the case note and close</t>
         </is>
       </c>
-      <c r="F24" s="15" t="n">
+      <c r="F24" s="17" t="n">
         <v>29</v>
       </c>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="G24" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="H24" s="16" t="inlineStr">
         <is>
           <t>Adjustment amount</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>BA-2204</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n">
+      <c r="B25" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>Find the adjustment on the account</t>
         </is>
       </c>
-      <c r="F25" s="15" t="n">
+      <c r="F25" s="17" t="n">
         <v>33</v>
       </c>
-      <c r="G25" s="14" t="inlineStr">
+      <c r="G25" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="H25" s="16" t="inlineStr">
         <is>
           <t>Account number</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>BA-2204</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
+      <c r="B26" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Payment gateway</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>Check whether the refund has actually posted</t>
         </is>
       </c>
-      <c r="F26" s="15" t="n">
+      <c r="F26" s="17" t="n">
         <v>44</v>
       </c>
-      <c r="G26" s="14" t="inlineStr">
+      <c r="G26" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H26" s="14" t="inlineStr">
+      <c r="H26" s="16" t="inlineStr">
         <is>
           <t>Transaction ID</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>BA-2204</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
+      <c r="B27" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>Payment gateway</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>Record the posting reference against the adjustment</t>
         </is>
       </c>
-      <c r="F27" s="15" t="n">
+      <c r="F27" s="17" t="n">
         <v>21</v>
       </c>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="G27" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr">
+      <c r="H27" s="16" t="inlineStr">
         <is>
           <t>Posting reference</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>BA-2204</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>Write the case note and close</t>
         </is>
       </c>
-      <c r="F28" s="15" t="n">
+      <c r="F28" s="17" t="n">
         <v>26</v>
       </c>
-      <c r="G28" s="14" t="inlineStr">
+      <c r="G28" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H28" s="14" t="inlineStr">
+      <c r="H28" s="16" t="inlineStr">
         <is>
           <t>Adjustment amount</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>BA-2205</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>Find the adjustment on the account</t>
         </is>
       </c>
-      <c r="F29" s="15" t="n">
+      <c r="F29" s="17" t="n">
         <v>29</v>
       </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G29" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="H29" s="16" t="inlineStr">
         <is>
           <t>Account number</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>BA-2205</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
+      <c r="B30" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Payment gateway</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>Check whether the refund has actually posted</t>
         </is>
       </c>
-      <c r="F30" s="15" t="n">
+      <c r="F30" s="17" t="n">
         <v>52</v>
       </c>
-      <c r="G30" s="14" t="inlineStr">
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H30" s="14" t="inlineStr">
+      <c r="H30" s="16" t="inlineStr">
         <is>
           <t>Transaction ID</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>BA-2205</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
+      <c r="B31" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>Payment gateway</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>Record the posting reference against the adjustment</t>
         </is>
       </c>
-      <c r="F31" s="15" t="n">
+      <c r="F31" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="G31" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="H31" s="16" t="inlineStr">
         <is>
           <t>Posting reference</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>BA-2205</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
+      <c r="B32" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>Write the case note and close</t>
         </is>
       </c>
-      <c r="F32" s="15" t="n">
+      <c r="F32" s="17" t="n">
         <v>31</v>
       </c>
-      <c r="G32" s="14" t="inlineStr">
+      <c r="G32" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H32" s="14" t="inlineStr">
+      <c r="H32" s="16" t="inlineStr">
         <is>
           <t>Adjustment amount</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>BA-2206</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
+      <c r="B33" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>Find the adjustment on the account</t>
         </is>
       </c>
-      <c r="F33" s="15" t="n">
+      <c r="F33" s="17" t="n">
         <v>35</v>
       </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="G33" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr">
+      <c r="H33" s="16" t="inlineStr">
         <is>
           <t>Account number</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>BA-2206</t>
         </is>
       </c>
-      <c r="B34" s="14" t="n">
+      <c r="B34" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Payment gateway</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>Check whether the refund has actually posted</t>
         </is>
       </c>
-      <c r="F34" s="15" t="n">
+      <c r="F34" s="17" t="n">
         <v>39</v>
       </c>
-      <c r="G34" s="14" t="inlineStr">
+      <c r="G34" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="H34" s="16" t="inlineStr">
         <is>
           <t>Transaction ID</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>BA-2206</t>
         </is>
       </c>
-      <c r="B35" s="14" t="n">
+      <c r="B35" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>Payment gateway</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>Record the posting reference against the adjustment</t>
         </is>
       </c>
-      <c r="F35" s="15" t="n">
+      <c r="F35" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="G35" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr">
+      <c r="H35" s="16" t="inlineStr">
         <is>
           <t>Posting reference</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>BA-2206</t>
         </is>
       </c>
-      <c r="B36" s="14" t="n">
+      <c r="B36" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="D36" s="14" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>Write the case note and close</t>
         </is>
       </c>
-      <c r="F36" s="15" t="n">
+      <c r="F36" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="G36" s="14" t="inlineStr">
+      <c r="G36" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H36" s="14" t="inlineStr">
+      <c r="H36" s="16" t="inlineStr">
         <is>
           <t>Adjustment amount</t>
         </is>
       </c>
     </row>
     <row r="37" ht="66" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Time the hop, not the task. The seconds here are the ones between leaving one screen and being able to work in the next — the load, the second login, the search that finds the account again. The work the agent does once they arrive is not a hop and belongs in the handle time above. DATA RE-KEYED means the agent typed something into the second system that the first one already knew, which is both the waste and the defect: every re-key is a chance to mistype an account number.</t>
         </is>
       </c>
-      <c r="J37" s="16" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>HOW TO READ IT.  One bar per contact, so the shape tells you whether the swivel is universal or concentrated. Even bars mean every contact pays it and the fix is worth the whole volume; a few tall bars mean a subset of cases is doing something the others are not, and that subset is the thing to define.
 SO:  Even bars mean fix it for everyone and size the benefit on full volume. A few tall bars mean define what those contacts have in common before building anything.</t>
@@ -2087,54 +2121,54 @@
       </c>
     </row>
     <row r="38"/>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>STEP 1 — how much of each contact went on moving between systems  ·  Key:
-• Share of handle time = the swivel measured against the whole contact, which is the number to take to anyone who owns the handle-time target. Where 'share of hop time' ranks the pairs against each other, this one says what the hopping costs overall — the same seconds against the 412-second baseline rather than against the other hops</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="n"/>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="7" t="n"/>
+• Share of handle time = the swivel measured against the whole contact, which is the number to take to anyone who owns the handle-time target.</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="9" t="n"/>
+      <c r="H39" s="9" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="B40" s="13" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>Contact ref</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>Seconds in hops</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>Share of handle time</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>Hops</t>
         </is>
       </c>
-      <c r="F40" s="13" t="inlineStr">
+      <c r="F40" s="15" t="inlineStr">
         <is>
           <t>Hops that re-keyed data</t>
         </is>
       </c>
-      <c r="G40" s="13" t="inlineStr"/>
-      <c r="H40" s="13" t="inlineStr"/>
+      <c r="G40" s="15" t="inlineStr"/>
+      <c r="H40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2142,24 +2176,24 @@
           <t>Contact</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>BA-2201</t>
         </is>
       </c>
-      <c r="C41" s="18">
+      <c r="C41" s="19">
         <f>SUMIF($A$13:$A$36,$B41,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="20">
         <f>IFERROR(C41/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E41" s="20">
+      <c r="E41" s="21">
         <f>COUNTIF($A$13:$A$36,$B41)</f>
         <v/>
       </c>
-      <c r="F41" s="20">
+      <c r="F41" s="21">
         <f>COUNTIFS($A$13:$A$36,$B41,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
@@ -2170,24 +2204,24 @@
           <t>Contact</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>BA-2202</t>
         </is>
       </c>
-      <c r="C42" s="18">
+      <c r="C42" s="19">
         <f>SUMIF($A$13:$A$36,$B42,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="20">
         <f>IFERROR(C42/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E42" s="20">
+      <c r="E42" s="21">
         <f>COUNTIF($A$13:$A$36,$B42)</f>
         <v/>
       </c>
-      <c r="F42" s="20">
+      <c r="F42" s="21">
         <f>COUNTIFS($A$13:$A$36,$B42,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
@@ -2198,24 +2232,24 @@
           <t>Contact</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>BA-2203</t>
         </is>
       </c>
-      <c r="C43" s="18">
+      <c r="C43" s="19">
         <f>SUMIF($A$13:$A$36,$B43,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="20">
         <f>IFERROR(C43/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E43" s="20">
+      <c r="E43" s="21">
         <f>COUNTIF($A$13:$A$36,$B43)</f>
         <v/>
       </c>
-      <c r="F43" s="20">
+      <c r="F43" s="21">
         <f>COUNTIFS($A$13:$A$36,$B43,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
@@ -2226,24 +2260,24 @@
           <t>Contact</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>BA-2204</t>
         </is>
       </c>
-      <c r="C44" s="18">
+      <c r="C44" s="19">
         <f>SUMIF($A$13:$A$36,$B44,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="20">
         <f>IFERROR(C44/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E44" s="20">
+      <c r="E44" s="21">
         <f>COUNTIF($A$13:$A$36,$B44)</f>
         <v/>
       </c>
-      <c r="F44" s="20">
+      <c r="F44" s="21">
         <f>COUNTIFS($A$13:$A$36,$B44,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
@@ -2254,24 +2288,24 @@
           <t>Contact</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>BA-2205</t>
         </is>
       </c>
-      <c r="C45" s="18">
+      <c r="C45" s="19">
         <f>SUMIF($A$13:$A$36,$B45,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="20">
         <f>IFERROR(C45/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E45" s="20">
+      <c r="E45" s="21">
         <f>COUNTIF($A$13:$A$36,$B45)</f>
         <v/>
       </c>
-      <c r="F45" s="20">
+      <c r="F45" s="21">
         <f>COUNTIFS($A$13:$A$36,$B45,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
@@ -2282,30 +2316,30 @@
           <t>Contact</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>BA-2206</t>
         </is>
       </c>
-      <c r="C46" s="18">
+      <c r="C46" s="19">
         <f>SUMIF($A$13:$A$36,$B46,$F$13:$F$36)</f>
         <v/>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="20">
         <f>IFERROR(C46/$B$7,"")</f>
         <v/>
       </c>
-      <c r="E46" s="20">
+      <c r="E46" s="21">
         <f>COUNTIF($A$13:$A$36,$B46)</f>
         <v/>
       </c>
-      <c r="F46" s="20">
+      <c r="F46" s="21">
         <f>COUNTIFS($A$13:$A$36,$B46,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="45" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>Look at the spread before you quote the average. If one contact carries most of the hopping you have found an exception to investigate, not a process to redesign — and a business case built on the mean would be wrong in the direction that gets it withdrawn.</t>
         </is>
@@ -2313,430 +2347,430 @@
     </row>
     <row r="48"/>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>STEP 2 — what the hopping costs across a year</t>
         </is>
       </c>
-      <c r="B49" s="7" t="n"/>
-      <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
-      <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7" t="n"/>
-      <c r="G49" s="7" t="n"/>
-      <c r="H49" s="7" t="n"/>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="n"/>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>Contacts observed</t>
         </is>
       </c>
-      <c r="B50" s="20">
+      <c r="B50" s="21">
         <f>COUNTA($B$41:$B$46)</f>
         <v/>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>Six is enough to size a problem and nowhere near enough to price one. Treat everything below as an order of magnitude until you have watched thirty.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>Hops logged</t>
         </is>
       </c>
-      <c r="B51" s="20">
+      <c r="B51" s="21">
         <f>SUM($E$41:$E$46)</f>
         <v/>
       </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>Every move, across every contact you watched.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>Hops per contact</t>
         </is>
       </c>
-      <c r="B52" s="21">
+      <c r="B52" s="22">
         <f>IFERROR(B51/B50,"")</f>
         <v/>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>The number people remember. It is also the one that makes a process owner uncomfortable enough to look at the log.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>Seconds per contact spent hopping</t>
         </is>
       </c>
-      <c r="B53" s="20">
+      <c r="B53" s="21">
         <f>IFERROR(SUM($C$41:$C$46)/B50,"")</f>
         <v/>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C53" s="12" t="inlineStr">
         <is>
           <t>Total hop time divided by contacts observed.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>Share of handle time</t>
         </is>
       </c>
-      <c r="B54" s="19">
+      <c r="B54" s="20">
         <f>IFERROR(B53/B7,"")</f>
         <v/>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C54" s="12" t="inlineStr">
         <is>
           <t>Against the platform's mean handle time above, not against the contacts you watched — an observed agent works faster, and the share would flatter you.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>Share of hops that re-key data</t>
         </is>
       </c>
-      <c r="B55" s="19">
+      <c r="B55" s="20">
         <f>IFERROR(SUM($F$41:$F$46)/B51,"")</f>
         <v/>
       </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="C55" s="12" t="inlineStr">
         <is>
           <t>The part of the waste that is also a defect risk. A hop that carries data across by hand can carry it across wrong.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>Agent hours a year spent hopping</t>
         </is>
       </c>
-      <c r="B56" s="18">
+      <c r="B56" s="19">
         <f>IFERROR(B53*B8/3600,"")</f>
         <v/>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C56" s="12" t="inlineStr">
         <is>
           <t>Seconds per contact times contacts a year. This is capacity, not cash.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>What that time costs a year</t>
         </is>
       </c>
-      <c r="B57" s="22">
+      <c r="B57" s="23">
         <f>IFERROR(B56*B9,"")</f>
         <v/>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C57" s="12" t="inlineStr">
         <is>
           <t>Hours at the loaded rate. It becomes a saving only when something is harvested — 01-project-charter.md will not accept it without a named mechanism.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="105" customHeight="1">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>The tool library says to expect 15-30% of handle time here. Treat that as a rule of thumb to test, not a published benchmark to be judged against: it is the range the method usually turns up, and it is not evidence about your queue. What decides whether there is a project is the cost on the line above and how many of these hops somebody who knows the systems believes are avoidable. A queue at a fifth of handle time where every hop is unavoidable has nothing in it; one at eight per cent where half the hops exist only because two systems were never joined up has a great deal.</t>
         </is>
       </c>
     </row>
     <row r="59"/>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" s="17" t="inlineStr">
+    <row r="60" ht="36" customHeight="1">
+      <c r="A60" s="18" t="inlineStr">
         <is>
           <t>STEP 3 — which hop to attack  ·  Key:
-• Share of hop time = that system pair's seconds as a percentage of all the time spent moving between systems — a share of the SWIVEL, not of the contact. Case tool to Billing platform takes 198 of the 737 logged seconds, 26.9% (E62, G62), so a third of the swivelling happens on one pair. It is the column that says which integration to build first</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="n"/>
-      <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="n"/>
-      <c r="E60" s="7" t="n"/>
-      <c r="F60" s="7" t="n"/>
-      <c r="G60" s="7" t="n"/>
-      <c r="H60" s="7" t="n"/>
+• Share of hop time = that system pair's seconds as a percentage of all the time spent moving between systems — a share of the SWIVEL, not of the contact.</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="n"/>
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="9" t="n"/>
+      <c r="E60" s="9" t="n"/>
+      <c r="F60" s="9" t="n"/>
+      <c r="G60" s="9" t="n"/>
+      <c r="H60" s="9" t="n"/>
     </row>
     <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="13" t="inlineStr">
+      <c r="A61" s="15" t="inlineStr">
         <is>
           <t>From system</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B61" s="15" t="inlineStr">
         <is>
           <t>To system</t>
         </is>
       </c>
-      <c r="C61" s="13" t="inlineStr">
+      <c r="C61" s="15" t="inlineStr">
         <is>
           <t>The pair</t>
         </is>
       </c>
-      <c r="D61" s="13" t="inlineStr">
+      <c r="D61" s="15" t="inlineStr">
         <is>
           <t>Hops</t>
         </is>
       </c>
-      <c r="E61" s="13" t="inlineStr">
+      <c r="E61" s="15" t="inlineStr">
         <is>
           <t>Total seconds</t>
         </is>
       </c>
-      <c r="F61" s="13" t="inlineStr">
+      <c r="F61" s="15" t="inlineStr">
         <is>
           <t>Seconds per contact</t>
         </is>
       </c>
-      <c r="G61" s="13" t="inlineStr">
+      <c r="G61" s="15" t="inlineStr">
         <is>
           <t>Share of hop time</t>
         </is>
       </c>
-      <c r="H61" s="13" t="inlineStr">
+      <c r="H61" s="15" t="inlineStr">
         <is>
           <t>Any re-keying?</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="14" t="inlineStr">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="B62" s="14" t="inlineStr">
+      <c r="B62" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="C62" s="23">
+      <c r="C62" s="24">
         <f>IF($A62="","",$A62&amp;" → "&amp;$B62)</f>
         <v/>
       </c>
-      <c r="D62" s="20">
+      <c r="D62" s="21">
         <f>COUNTIFS($C$13:$C$36,$A62,$D$13:$D$36,$B62)</f>
         <v/>
       </c>
-      <c r="E62" s="18">
+      <c r="E62" s="19">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A62,$D$13:$D$36,$B62)</f>
         <v/>
       </c>
-      <c r="F62" s="21">
+      <c r="F62" s="22">
         <f>IFERROR(E62/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G62" s="19">
+      <c r="G62" s="20">
         <f>IFERROR(E62/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H62" s="23">
+      <c r="H62" s="24">
         <f>IF(COUNTIFS($C$13:$C$36,$A62,$D$13:$D$36,$B62,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="14" t="inlineStr">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="B63" s="14" t="inlineStr">
+      <c r="B63" s="16" t="inlineStr">
         <is>
           <t>Payment gateway</t>
         </is>
       </c>
-      <c r="C63" s="23">
+      <c r="C63" s="24">
         <f>IF($A63="","",$A63&amp;" → "&amp;$B63)</f>
         <v/>
       </c>
-      <c r="D63" s="20">
+      <c r="D63" s="21">
         <f>COUNTIFS($C$13:$C$36,$A63,$D$13:$D$36,$B63)</f>
         <v/>
       </c>
-      <c r="E63" s="18">
+      <c r="E63" s="19">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A63,$D$13:$D$36,$B63)</f>
         <v/>
       </c>
-      <c r="F63" s="21">
+      <c r="F63" s="22">
         <f>IFERROR(E63/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G63" s="19">
+      <c r="G63" s="20">
         <f>IFERROR(E63/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H63" s="23">
+      <c r="H63" s="24">
         <f>IF(COUNTIFS($C$13:$C$36,$A63,$D$13:$D$36,$B63,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="14" t="inlineStr">
+      <c r="A64" s="16" t="inlineStr">
         <is>
           <t>Payment gateway</t>
         </is>
       </c>
-      <c r="B64" s="14" t="inlineStr">
+      <c r="B64" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="C64" s="23">
+      <c r="C64" s="24">
         <f>IF($A64="","",$A64&amp;" → "&amp;$B64)</f>
         <v/>
       </c>
-      <c r="D64" s="20">
+      <c r="D64" s="21">
         <f>COUNTIFS($C$13:$C$36,$A64,$D$13:$D$36,$B64)</f>
         <v/>
       </c>
-      <c r="E64" s="18">
+      <c r="E64" s="19">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A64,$D$13:$D$36,$B64)</f>
         <v/>
       </c>
-      <c r="F64" s="21">
+      <c r="F64" s="22">
         <f>IFERROR(E64/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G64" s="19">
+      <c r="G64" s="20">
         <f>IFERROR(E64/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H64" s="23">
+      <c r="H64" s="24">
         <f>IF(COUNTIFS($C$13:$C$36,$A64,$D$13:$D$36,$B64,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14" t="inlineStr">
+      <c r="A65" s="16" t="inlineStr">
         <is>
           <t>Billing platform</t>
         </is>
       </c>
-      <c r="B65" s="14" t="inlineStr">
+      <c r="B65" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="C65" s="23">
+      <c r="C65" s="24">
         <f>IF($A65="","",$A65&amp;" → "&amp;$B65)</f>
         <v/>
       </c>
-      <c r="D65" s="20">
+      <c r="D65" s="21">
         <f>COUNTIFS($C$13:$C$36,$A65,$D$13:$D$36,$B65)</f>
         <v/>
       </c>
-      <c r="E65" s="18">
+      <c r="E65" s="19">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A65,$D$13:$D$36,$B65)</f>
         <v/>
       </c>
-      <c r="F65" s="21">
+      <c r="F65" s="22">
         <f>IFERROR(E65/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G65" s="19">
+      <c r="G65" s="20">
         <f>IFERROR(E65/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H65" s="23">
+      <c r="H65" s="24">
         <f>IF(COUNTIFS($C$13:$C$36,$A65,$D$13:$D$36,$B65,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="14" t="inlineStr">
+      <c r="A66" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="B66" s="14" t="inlineStr">
+      <c r="B66" s="16" t="inlineStr">
         <is>
           <t>Knowledge base</t>
         </is>
       </c>
-      <c r="C66" s="23">
+      <c r="C66" s="24">
         <f>IF($A66="","",$A66&amp;" → "&amp;$B66)</f>
         <v/>
       </c>
-      <c r="D66" s="20">
+      <c r="D66" s="21">
         <f>COUNTIFS($C$13:$C$36,$A66,$D$13:$D$36,$B66)</f>
         <v/>
       </c>
-      <c r="E66" s="18">
+      <c r="E66" s="19">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A66,$D$13:$D$36,$B66)</f>
         <v/>
       </c>
-      <c r="F66" s="21">
+      <c r="F66" s="22">
         <f>IFERROR(E66/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G66" s="19">
+      <c r="G66" s="20">
         <f>IFERROR(E66/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H66" s="23">
+      <c r="H66" s="24">
         <f>IF(COUNTIFS($C$13:$C$36,$A66,$D$13:$D$36,$B66,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14" t="inlineStr">
+      <c r="A67" s="16" t="inlineStr">
         <is>
           <t>Knowledge base</t>
         </is>
       </c>
-      <c r="B67" s="14" t="inlineStr">
+      <c r="B67" s="16" t="inlineStr">
         <is>
           <t>Case tool</t>
         </is>
       </c>
-      <c r="C67" s="23">
+      <c r="C67" s="24">
         <f>IF($A67="","",$A67&amp;" → "&amp;$B67)</f>
         <v/>
       </c>
-      <c r="D67" s="20">
+      <c r="D67" s="21">
         <f>COUNTIFS($C$13:$C$36,$A67,$D$13:$D$36,$B67)</f>
         <v/>
       </c>
-      <c r="E67" s="18">
+      <c r="E67" s="19">
         <f>SUMIFS($F$13:$F$36,$C$13:$C$36,$A67,$D$13:$D$36,$B67)</f>
         <v/>
       </c>
-      <c r="F67" s="21">
+      <c r="F67" s="22">
         <f>IFERROR(E67/$B$50,"")</f>
         <v/>
       </c>
-      <c r="G67" s="19">
+      <c r="G67" s="20">
         <f>IFERROR(E67/SUM($E$62:$E$67),"")</f>
         <v/>
       </c>
-      <c r="H67" s="23">
+      <c r="H67" s="24">
         <f>IF(COUNTIFS($C$13:$C$36,$A67,$D$13:$D$36,$B67,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="60" customHeight="1">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>One row per direction, because they are different problems: leaving the case tool for the billing platform is a lookup, and coming back is a write-up. Add a pair by inserting a row inside this block — the formulas above and below it will follow. Sort the block by total seconds if you want the chart ranked; it plots the order you typed.</t>
         </is>
@@ -2744,69 +2778,69 @@
     </row>
     <row r="69"/>
     <row r="70">
-      <c r="A70" s="6" t="inlineStr">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>STEP 4 — the verdict</t>
         </is>
       </c>
-      <c r="B70" s="7" t="n"/>
-      <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
-      <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
+      <c r="B70" s="9" t="n"/>
+      <c r="C70" s="9" t="n"/>
+      <c r="D70" s="9" t="n"/>
+      <c r="E70" s="9" t="n"/>
+      <c r="F70" s="9" t="n"/>
+      <c r="G70" s="9" t="n"/>
+      <c r="H70" s="9" t="n"/>
     </row>
     <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>The pair costing the most time</t>
         </is>
       </c>
-      <c r="B71" s="23">
+      <c r="B71" s="24">
         <f>IFERROR(INDEX($C$62:$C$67,MATCH(MAX($E$62:$E$67),$E$62:$E$67,0)),"")</f>
         <v/>
       </c>
-      <c r="C71" s="10" t="inlineStr">
+      <c r="C71" s="12" t="inlineStr">
         <is>
           <t>Where an integration, a deep link or a copied field would buy the most. It is not always the slowest single hop — a fast hop made on every contact beats a slow one made on a tenth of them.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>What that one pair costs a year</t>
         </is>
       </c>
-      <c r="B72" s="22">
+      <c r="B72" s="23">
         <f>IFERROR(MAX($E$62:$E$67)/B50*B8/3600*B9,"")</f>
         <v/>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C72" s="12" t="inlineStr">
         <is>
           <t>Seconds per contact on that pair, annualised at the loaded rate. Take this to the system owner, not the contact-centre manager — it is their backlog it belongs in.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="8" t="inlineStr">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>Does that pair re-key data?</t>
         </is>
       </c>
-      <c r="B73" s="23">
+      <c r="B73" s="24">
         <f>IFERROR(INDEX($H$62:$H$67,MATCH(MAX($E$62:$E$67),$E$62:$E$67,0)),"")</f>
         <v/>
       </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="C73" s="12" t="inlineStr">
         <is>
           <t>If yes, the case is stronger than the time alone: you are also arguing about accuracy, and a mistyped account number costs far more than the forty seconds it took to type.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="60" customHeight="1">
-      <c r="A74" s="10" t="inlineStr">
+      <c r="A74" s="12" t="inlineStr">
         <is>
           <t>Removing a hop does not return all of its seconds. Some of that time is the agent thinking, and thinking moves to whatever is on the screen next. Halve the figure above before you put it in a charter, say in the charter that you halved it, and then prove the real number in a pilot (16-pilot-protocol.md) against a control group.</t>
         </is>

--- a/templates/32-system-hop.xlsx
+++ b/templates/32-system-hop.xlsx
@@ -295,6 +295,40 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Mean — a pair above this line is worth an integration</v>
+          </tx>
+          <spPr>
+            <a:ln w="18000">
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Hop log'!$I$62:$I$67</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -323,6 +357,9 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -343,7 +380,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Seconds spent hopping, contact by contact</a:t>
+              <a:t>Hop time is not evenly spread — a few contacts carry it</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -386,6 +423,40 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Mean — the contacts above it are the ones to watch</v>
+          </tx>
+          <spPr>
+            <a:ln w="18000">
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Hop log'!$I$41:$I$46</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -416,6 +487,9 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -2169,6 +2243,11 @@
       </c>
       <c r="G40" s="15" t="inlineStr"/>
       <c r="H40" s="15" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>Mean seconds per contact</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2197,6 +2276,10 @@
         <f>COUNTIFS($A$13:$A$36,$B41,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
+      <c r="I41" s="7">
+        <f>IF(COUNT($C$41:$C$46)=0,"",AVERAGE($C$41:$C$46))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2225,6 +2308,10 @@
         <f>COUNTIFS($A$13:$A$36,$B42,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
+      <c r="I42" s="7">
+        <f>IF(COUNT($C$41:$C$46)=0,"",AVERAGE($C$41:$C$46))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2253,6 +2340,10 @@
         <f>COUNTIFS($A$13:$A$36,$B43,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
+      <c r="I43" s="7">
+        <f>IF(COUNT($C$41:$C$46)=0,"",AVERAGE($C$41:$C$46))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2281,6 +2372,10 @@
         <f>COUNTIFS($A$13:$A$36,$B44,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
+      <c r="I44" s="7">
+        <f>IF(COUNT($C$41:$C$46)=0,"",AVERAGE($C$41:$C$46))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2309,6 +2404,10 @@
         <f>COUNTIFS($A$13:$A$36,$B45,$G$13:$G$36,"Y")</f>
         <v/>
       </c>
+      <c r="I45" s="7">
+        <f>IF(COUNT($C$41:$C$46)=0,"",AVERAGE($C$41:$C$46))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2335,6 +2434,10 @@
       </c>
       <c r="F46" s="21">
         <f>COUNTIFS($A$13:$A$36,$B46,$G$13:$G$36,"Y")</f>
+        <v/>
+      </c>
+      <c r="I46" s="7">
+        <f>IF(COUNT($C$41:$C$46)=0,"",AVERAGE($C$41:$C$46))</f>
         <v/>
       </c>
     </row>
@@ -2552,6 +2655,11 @@
           <t>Any re-keying?</t>
         </is>
       </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>Mean seconds per pair</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
@@ -2588,6 +2696,10 @@
         <f>IF(COUNTIFS($C$13:$C$36,$A62,$D$13:$D$36,$B62,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
+      <c r="I62" s="7">
+        <f>IF(COUNT($E$62:$E$67)=0,"",AVERAGE($E$62:$E$67))</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
@@ -2624,6 +2736,10 @@
         <f>IF(COUNTIFS($C$13:$C$36,$A63,$D$13:$D$36,$B63,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
+      <c r="I63" s="7">
+        <f>IF(COUNT($E$62:$E$67)=0,"",AVERAGE($E$62:$E$67))</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
@@ -2660,6 +2776,10 @@
         <f>IF(COUNTIFS($C$13:$C$36,$A64,$D$13:$D$36,$B64,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
+      <c r="I64" s="7">
+        <f>IF(COUNT($E$62:$E$67)=0,"",AVERAGE($E$62:$E$67))</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
@@ -2696,6 +2816,10 @@
         <f>IF(COUNTIFS($C$13:$C$36,$A65,$D$13:$D$36,$B65,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
+      <c r="I65" s="7">
+        <f>IF(COUNT($E$62:$E$67)=0,"",AVERAGE($E$62:$E$67))</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
@@ -2732,6 +2856,10 @@
         <f>IF(COUNTIFS($C$13:$C$36,$A66,$D$13:$D$36,$B66,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
         <v/>
       </c>
+      <c r="I66" s="7">
+        <f>IF(COUNT($E$62:$E$67)=0,"",AVERAGE($E$62:$E$67))</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
@@ -2766,6 +2894,10 @@
       </c>
       <c r="H67" s="24">
         <f>IF(COUNTIFS($C$13:$C$36,$A67,$D$13:$D$36,$B67,$G$13:$G$36,"Y")&gt;0,"yes","no")</f>
+        <v/>
+      </c>
+      <c r="I67" s="7">
+        <f>IF(COUNT($E$62:$E$67)=0,"",AVERAGE($E$62:$E$67))</f>
         <v/>
       </c>
     </row>
